--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/CI/0.2/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/CI/0.2/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CI\0.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingADV\CI\0.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CAFCE1-5FAC-4CD7-B259-147E035D7C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434C36A0-F486-42BD-A9BE-A6792262134E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,8 +140,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -461,69 +462,69 @@
       <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2">
-        <v>17.850000000000001</v>
-      </c>
-      <c r="C2">
-        <v>2.0282723902101756</v>
-      </c>
-      <c r="D2">
-        <v>15.9</v>
-      </c>
-      <c r="E2">
-        <v>2.6331223544175351</v>
-      </c>
-      <c r="F2">
-        <v>29.65</v>
-      </c>
-      <c r="G2">
-        <v>3.6972211787292903</v>
-      </c>
-      <c r="H2">
-        <v>21.133333333333333</v>
-      </c>
-      <c r="I2">
-        <v>1.8355205807805957</v>
-      </c>
-      <c r="J2">
-        <v>5.5833333333333313</v>
-      </c>
-      <c r="K2">
-        <v>1.305851030393687</v>
+      <c r="B2" s="1">
+        <v>16.7222222222222</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2.635231383473652</v>
+      </c>
+      <c r="D2" s="1">
+        <v>22.166666666666668</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5.2380817099392409</v>
+      </c>
+      <c r="F2" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3.2691742076555053</v>
+      </c>
+      <c r="H2" s="1">
+        <v>23.462962962962958</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2.8096779394544562</v>
+      </c>
+      <c r="J2" s="1">
+        <v>7.5740740740740744</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0.90948364131916359</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>16.25</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>2.4748737341529163</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>15</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>2.8284271247461903</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>28.25</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>2.4748737341529163</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>19.833333333333336</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <v>0.94280904158206247</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <v>6.0833333333333339</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0.11785113019775875</v>
       </c>
     </row>
@@ -531,34 +532,34 @@
       <c r="A4" t="s">
         <v>21</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>18.25</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1.7677669529663689</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>14</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>2.1213203435596424</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>27.25</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>3.8890872965260113</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>19.833333333333336</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <v>2.5927248643506751</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <v>5.8333333333333339</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0.47140452079103251</v>
       </c>
     </row>
@@ -2075,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F52E050-0D53-43C0-B5FC-AD6D7416AA3A}">
-  <dimension ref="B1:AG11"/>
+  <dimension ref="B1:AG10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="2:33" x14ac:dyDescent="0.3">
@@ -2130,186 +2131,186 @@
     </row>
     <row r="2" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J2">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L2">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="M2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="N2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="Q2">
         <f>AVERAGE(C2:D2)</f>
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="R2">
         <f>AVERAGE(H2:I2)</f>
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="S2">
         <f>AVERAGE(M2:N2)</f>
-        <v>32.5</v>
+        <v>26</v>
       </c>
       <c r="T2">
         <f>AVERAGE(Q2:S2)</f>
-        <v>22.333333333333332</v>
+        <v>20.5</v>
       </c>
       <c r="U2">
         <f>MIN(Q2:S2)</f>
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="V2">
         <f>T2-U2</f>
-        <v>6.8333333333333321</v>
+        <v>6.5</v>
       </c>
       <c r="X2">
-        <f>AVERAGE(Q2:Q11)</f>
-        <v>17.850000000000001</v>
+        <f>AVERAGE(Q2:Q10)</f>
+        <v>16.722222222222221</v>
       </c>
       <c r="Y2">
-        <f>_xlfn.STDEV.S(Q2:Q11)</f>
-        <v>2.0282723902101756</v>
+        <f>_xlfn.STDEV.S(Q2:Q10)</f>
+        <v>2.635231383473652</v>
       </c>
       <c r="Z2">
-        <f>AVERAGE(R2:R11)</f>
-        <v>15.9</v>
+        <f>AVERAGE(R2:R10)</f>
+        <v>22.166666666666668</v>
       </c>
       <c r="AA2">
-        <f>_xlfn.STDEV.S(R2:R11)</f>
-        <v>2.6331223544175351</v>
+        <f>_xlfn.STDEV.S(R2:R10)</f>
+        <v>5.2380817099392409</v>
       </c>
       <c r="AB2">
-        <f>AVERAGE(S2:S11)</f>
-        <v>29.65</v>
+        <f>AVERAGE(S2:S10)</f>
+        <v>31.5</v>
       </c>
       <c r="AC2">
-        <f>_xlfn.STDEV.S(S2:S11)</f>
-        <v>3.6972211787292903</v>
+        <f>_xlfn.STDEV.S(S2:S10)</f>
+        <v>3.2691742076555053</v>
       </c>
       <c r="AD2">
-        <f>AVERAGE(T2:T11)</f>
-        <v>21.133333333333333</v>
+        <f>AVERAGE(T2:T10)</f>
+        <v>23.462962962962958</v>
       </c>
       <c r="AE2">
-        <f>_xlfn.STDEV.S(T2:T11)</f>
-        <v>1.8355205807805957</v>
+        <f>_xlfn.STDEV.S(T2:T10)</f>
+        <v>2.8096779394544562</v>
       </c>
       <c r="AF2">
-        <f>AVERAGE(V2:V11)</f>
-        <v>5.5833333333333313</v>
+        <f>AVERAGE(V2:V10)</f>
+        <v>7.5740740740740744</v>
       </c>
       <c r="AG2">
-        <f>_xlfn.STDEV.S(V2:V11)</f>
-        <v>1.305851030393687</v>
+        <f>_xlfn.STDEV.S(V2:V10)</f>
+        <v>0.90948364131916359</v>
       </c>
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G3">
+        <v>51</v>
+      </c>
+      <c r="H3">
+        <v>49</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>95</v>
+      </c>
+      <c r="L3">
+        <v>61</v>
+      </c>
+      <c r="M3">
+        <v>39</v>
+      </c>
+      <c r="N3">
+        <v>25</v>
+      </c>
+      <c r="O3">
         <v>75</v>
       </c>
-      <c r="H3">
-        <v>25</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>93</v>
-      </c>
-      <c r="L3">
-        <v>70</v>
-      </c>
-      <c r="M3">
-        <v>30</v>
-      </c>
-      <c r="N3">
-        <v>28</v>
-      </c>
-      <c r="O3">
-        <v>72</v>
-      </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q11" si="0">AVERAGE(C3:D3)</f>
-        <v>16.5</v>
+        <f t="shared" ref="Q3:Q10" si="0">AVERAGE(C3:D3)</f>
+        <v>17.5</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R11" si="1">AVERAGE(H3:I3)</f>
-        <v>16</v>
+        <f t="shared" ref="R3:R10" si="1">AVERAGE(H3:I3)</f>
+        <v>27</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S11" si="2">AVERAGE(M3:N3)</f>
-        <v>29</v>
+        <f t="shared" ref="S3:S10" si="2">AVERAGE(M3:N3)</f>
+        <v>32</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T11" si="3">AVERAGE(Q3:S3)</f>
-        <v>20.5</v>
+        <f t="shared" ref="T3:T10" si="3">AVERAGE(Q3:S3)</f>
+        <v>25.5</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U11" si="4">MIN(Q3:S3)</f>
-        <v>16</v>
+        <f t="shared" ref="U3:U10" si="4">MIN(Q3:S3)</f>
+        <v>17.5</v>
       </c>
       <c r="V3">
-        <f t="shared" ref="V3:V11" si="5">T3-U3</f>
-        <v>4.5</v>
+        <f t="shared" ref="V3:V10" si="5">T3-U3</f>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G4">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H4">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -2318,342 +2319,342 @@
         <v>92</v>
       </c>
       <c r="L4">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="M4">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="N4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O4">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="R4">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>22.5</v>
       </c>
       <c r="S4">
         <f t="shared" si="2"/>
-        <v>29.5</v>
+        <v>33</v>
       </c>
       <c r="T4">
         <f t="shared" si="3"/>
-        <v>21.833333333333332</v>
+        <v>24</v>
       </c>
       <c r="U4">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="V4">
         <f t="shared" si="5"/>
-        <v>3.8333333333333321</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B5">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L5">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N5">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>21.5</v>
       </c>
       <c r="R5">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="S5">
         <f t="shared" si="2"/>
-        <v>30.5</v>
+        <v>38</v>
       </c>
       <c r="T5">
         <f t="shared" si="3"/>
-        <v>20.833333333333332</v>
+        <v>28.833333333333332</v>
       </c>
       <c r="U5">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>21.5</v>
       </c>
       <c r="V5">
         <f t="shared" si="5"/>
-        <v>4.8333333333333321</v>
+        <v>7.3333333333333321</v>
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G6">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L6">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="S6">
         <f t="shared" si="2"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>21.333333333333332</v>
+        <v>21.5</v>
       </c>
       <c r="U6">
         <f t="shared" si="4"/>
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="V6">
         <f t="shared" si="5"/>
-        <v>5.8333333333333321</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G7">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L7">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N7">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="S7">
         <f t="shared" si="2"/>
-        <v>28.5</v>
+        <v>31.5</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>21.166666666666668</v>
+        <v>24</v>
       </c>
       <c r="U7">
         <f t="shared" si="4"/>
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="V7">
         <f t="shared" si="5"/>
-        <v>3.6666666666666679</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G8">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J8">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L8">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="M8">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="N8">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="O8">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="S8">
         <f t="shared" si="2"/>
-        <v>22.5</v>
+        <v>30.5</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>17.833333333333332</v>
+        <v>25.166666666666668</v>
       </c>
       <c r="U8">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="V8">
         <f t="shared" si="5"/>
-        <v>6.8333333333333321</v>
+        <v>8.1666666666666679</v>
       </c>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B9">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H9">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L9">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="M9">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N9">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="O9">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="Q9">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R9">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="S9">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>28.5</v>
       </c>
       <c r="T9">
         <f t="shared" si="3"/>
-        <v>21.333333333333332</v>
+        <v>20.5</v>
       </c>
       <c r="U9">
         <f t="shared" si="4"/>
@@ -2661,131 +2662,69 @@
       </c>
       <c r="V9">
         <f t="shared" si="5"/>
-        <v>7.3333333333333321</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B10">
+        <v>87</v>
+      </c>
+      <c r="C10">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>16</v>
+      </c>
+      <c r="E10">
         <v>84</v>
       </c>
-      <c r="C10">
-        <v>16</v>
-      </c>
-      <c r="D10">
-        <v>27</v>
-      </c>
-      <c r="E10">
-        <v>73</v>
-      </c>
       <c r="G10">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H10">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J10">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="L10">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M10">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N10">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="O10">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="Q10">
         <f t="shared" si="0"/>
-        <v>21.5</v>
+        <v>14.5</v>
       </c>
       <c r="R10">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="S10">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T10">
         <f t="shared" si="3"/>
-        <v>24.833333333333332</v>
+        <v>21.166666666666668</v>
       </c>
       <c r="U10">
         <f t="shared" si="4"/>
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="V10">
         <f t="shared" si="5"/>
-        <v>5.8333333333333321</v>
-      </c>
-    </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>81</v>
-      </c>
-      <c r="C11">
-        <v>19</v>
-      </c>
-      <c r="D11">
-        <v>21</v>
-      </c>
-      <c r="E11">
-        <v>79</v>
-      </c>
-      <c r="G11">
-        <v>80</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11">
-        <v>6</v>
-      </c>
-      <c r="J11">
-        <v>94</v>
-      </c>
-      <c r="L11">
-        <v>67</v>
-      </c>
-      <c r="M11">
-        <v>33</v>
-      </c>
-      <c r="N11">
-        <v>17</v>
-      </c>
-      <c r="O11">
-        <v>83</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="2"/>
-        <v>25</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="3"/>
-        <v>19.333333333333332</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="5"/>
-        <v>6.3333333333333321</v>
+        <v>6.6666666666666679</v>
       </c>
     </row>
   </sheetData>
